--- a/database/raw/math_models/50 Hz.xlsx
+++ b/database/raw/math_models/50 Hz.xlsx
@@ -5,15 +5,15 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="50 HZ Prueba 1 " sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="50 HZ Prueba 1" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="50 HZ Prueba 2" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="50 HZ Prueba 3" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'50 HZ Prueba 1 '!$A$1:$D$11</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'50 HZ Prueba 1'!$A$1:$D$11</definedName>
     <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'50 HZ Prueba 2'!$A$1:$D$10</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'50 HZ Prueba 3'!$A$1:$D$10</definedName>
   </definedNames>
@@ -137,20 +137,24 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -474,114 +478,114 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="3" t="n">
         <v>1400</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="3" t="n">
         <v>8.62</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="3" t="n">
         <v>9.36</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="4" t="n">
         <v>11.24</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="3" t="n">
         <v>1200</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="3" t="n">
         <v>6.87</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="3" t="n">
         <v>7.67</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="4" t="n">
         <v>12.97</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="3" t="n">
         <v>900</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="3" t="n">
         <v>5.57</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="3" t="n">
         <v>6.37</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="4" t="n">
         <v>13.76</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="3" t="n">
         <v>6.05</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="3" t="n">
         <v>6.85</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="4" t="n">
         <v>12.72</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="3" t="n">
         <v>750</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="3" t="n">
         <v>5.36</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="3" t="n">
         <v>6.21</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" s="4" t="n">
         <v>14.14</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="3" t="n">
         <v>600</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="3" t="n">
         <v>5.33</v>
       </c>
-      <c r="C7" s="0" t="n">
+      <c r="C7" s="3" t="n">
         <v>6.24</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="5" t="n">
         <v>14.26</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="3" t="n">
         <v>500</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="3" t="n">
         <v>5.02</v>
       </c>
-      <c r="C8" s="0" t="n">
+      <c r="C8" s="3" t="n">
         <v>6.95</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="D8" s="4" t="n">
         <v>13.58</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="3" t="n">
         <v>300</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="3" t="n">
         <v>4.91</v>
       </c>
-      <c r="C9" s="0" t="n">
+      <c r="C9" s="3" t="n">
         <v>5.83</v>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D9" s="6" t="n">
         <v>13.2</v>
       </c>
     </row>
@@ -622,100 +626,100 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="3" t="n">
         <v>1450</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="3" t="n">
         <v>8.3</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="3" t="n">
         <v>9.32</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="4" t="n">
         <v>10.67</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="3" t="n">
         <v>1200</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="3" t="n">
         <v>7.09</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="3" t="n">
         <v>8.07</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="4" t="n">
         <v>11.59</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="3" t="n">
         <v>6.52</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="3" t="n">
         <v>7.51</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="4" t="n">
         <v>12.44</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="3" t="n">
         <v>900</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="3" t="n">
         <v>5.69</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="3" t="n">
         <v>6.67</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="4" t="n">
         <v>12.27</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="3" t="n">
         <v>750</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="3" t="n">
         <v>5.34</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="3" t="n">
         <v>6.39</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="5" t="n">
         <v>13.28</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="3" t="n">
         <v>600</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="3" t="n">
         <v>5.1</v>
       </c>
-      <c r="C7" s="0" t="n">
+      <c r="C7" s="3" t="n">
         <v>6.18</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="4" t="n">
         <v>13.23</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="3" t="n">
         <v>500</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="3" t="n">
         <v>5.13</v>
       </c>
-      <c r="C8" s="0" t="n">
+      <c r="C8" s="3" t="n">
         <v>6.22</v>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" s="6" t="n">
         <v>13.5</v>
       </c>
     </row>
@@ -756,184 +760,184 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="3" t="n">
         <v>1450</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="3" t="n">
         <v>7.51</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="3" t="n">
         <v>8.96</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="4" t="n">
         <v>10.39</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="3" t="n">
         <v>1300</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="3" t="n">
         <v>7.3</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="3" t="n">
         <v>8.78</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="4" t="n">
         <v>10.97</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="3" t="n">
         <v>1200</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="3" t="n">
         <v>6.54</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="3" t="n">
         <v>8.01</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" s="4" t="n">
         <v>11.95</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="3" t="n">
         <v>1000</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="3" t="n">
         <v>6.12</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="3" t="n">
         <v>7.59</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" s="4" t="n">
         <v>12.19</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="3" t="n">
         <v>900</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="3" t="n">
         <v>5.12</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="3" t="n">
         <v>6.58</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="5" t="n">
         <v>12.7</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="3" t="n">
         <v>800</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="3" t="n">
         <v>4.72</v>
       </c>
-      <c r="C7" s="0" t="n">
+      <c r="C7" s="3" t="n">
         <v>6.25</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="D7" s="4" t="n">
         <v>12.32</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="3" t="n">
         <v>700</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="3" t="n">
         <v>4.67</v>
       </c>
-      <c r="C8" s="0" t="n">
+      <c r="C8" s="3" t="n">
         <v>6.25</v>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" s="6" t="n">
         <v>12.71</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="3" t="n">
         <v>600</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="3" t="n">
         <v>4.69</v>
       </c>
-      <c r="C9" s="0" t="n">
+      <c r="C9" s="3" t="n">
         <v>6.26</v>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D9" s="6" t="n">
         <v>11.71</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+      <c r="A10" s="3" t="n">
         <v>500</v>
       </c>
-      <c r="B10" s="0" t="n">
+      <c r="B10" s="3" t="n">
         <v>4.53</v>
       </c>
-      <c r="C10" s="0" t="n">
+      <c r="C10" s="3" t="n">
         <v>6.19</v>
       </c>
-      <c r="D10" s="5" t="n">
+      <c r="D10" s="6" t="n">
         <v>12.17</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+      <c r="A11" s="3" t="n">
         <v>400</v>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11" s="3" t="n">
         <v>4.36</v>
       </c>
-      <c r="C11" s="0" t="n">
+      <c r="C11" s="3" t="n">
         <v>5.93</v>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="D11" s="6" t="n">
         <v>11.48</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+      <c r="A12" s="3" t="n">
         <v>300</v>
       </c>
-      <c r="B12" s="0" t="n">
+      <c r="B12" s="3" t="n">
         <v>4.46</v>
       </c>
-      <c r="C12" s="0" t="n">
+      <c r="C12" s="3" t="n">
         <v>5.02</v>
       </c>
-      <c r="D12" s="5" t="n">
+      <c r="D12" s="6" t="n">
         <v>11.18</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
+      <c r="A13" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="B13" s="0" t="n">
+      <c r="B13" s="3" t="n">
         <v>4.36</v>
       </c>
-      <c r="C13" s="0" t="n">
+      <c r="C13" s="3" t="n">
         <v>5.88</v>
       </c>
-      <c r="D13" s="5" t="n">
+      <c r="D13" s="6" t="n">
         <v>11.02</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
+      <c r="A14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14" s="3" t="n">
         <v>7.94</v>
       </c>
-      <c r="C14" s="0" t="n">
+      <c r="C14" s="3" t="n">
         <v>9.5</v>
       </c>
-      <c r="D14" s="5" t="n">
+      <c r="D14" s="6" t="n">
         <v>10.83</v>
       </c>
     </row>
